--- a/tests/TC-01/results/teacher_timetables_even.xlsx
+++ b/tests/TC-01/results/teacher_timetables_even.xlsx
@@ -127,10 +127,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -648,8 +648,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>CS252
+Room: 101</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>CS252
+Room: 101</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -669,31 +679,51 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>CS252
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>CS252
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>CS252
+Room: 101</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>CS252
+Room: 101</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -703,30 +733,10 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>CS252
-Room: 102</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>CS252
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>CS252
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>CS252
-Room: 102</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -743,51 +753,31 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>CS252
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>CS252
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>CS252
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>CS252
-Room: 102</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -807,22 +797,17 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>CS252
+Room: 102</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>CS252
-Room: 102</t>
-        </is>
-      </c>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>CS252
-Room: 102</t>
-        </is>
-      </c>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
@@ -989,28 +974,23 @@
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 101</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>CS469
+Room: 102</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>CS469
+Room: 102</t>
+        </is>
+      </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -1023,46 +1003,31 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 101</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1072,10 +1037,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>CS469
+Room: 102</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>CS469
+Room: 102</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>CS469
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>CS469
+Room: 102</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -1092,41 +1077,36 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>CS469
-Room: 101</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 101</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1337,31 +1317,41 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>DA352
+Room: None</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>DA352
+Room: None</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1377,8 +1367,18 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>DA352
+Room: None</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>DA352
+Room: None</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
@@ -1391,46 +1391,46 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>DA352
 Room: None</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>DA352
 Room: None</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>DA352
 Room: None</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1453,24 +1453,9 @@
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>DA352
-Room: None</t>
-        </is>
-      </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>DA352
-Room: None</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="inlineStr">
-        <is>
-          <t>DA352
-Room: None</t>
-        </is>
-      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
@@ -1635,33 +1620,38 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CS253
+Room: None</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CS253
+Room: None</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>CS368
-Room: 102</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>CS368
-Room: 102</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>CS368
-Room: 102</t>
-        </is>
-      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>CS368
+Room: 101</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>CS368
+Room: 101</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -1671,46 +1661,51 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>CS368
-Room: None</t>
-        </is>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>CS368
-Room: None</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>CS368
-Room: None</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CS253
+Room: None</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CS253
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CS253
+Room: None</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CS253
+Room: None</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1720,54 +1715,29 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CS253
-Room: None</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CS253
-Room: None</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CS253
-Room: None</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CS253
-Room: None</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>CS368
-Room: None</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
+Room: 101</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>CS368
-Room: None</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>CS368
-Room: None</t>
-        </is>
-      </c>
+Room: 101</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
@@ -1775,51 +1745,46 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CS253
-Room: None</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CS253
-Room: None</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CS253
-Room: None</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CS253
-Room: None</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>CS368
+Room: 101</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>CS368
+Room: 101</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>CS368
+Room: 101</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1839,22 +1804,17 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CS253
+Room: None</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CS253
-Room: None</t>
-        </is>
-      </c>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CS253
-Room: None</t>
-        </is>
-      </c>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
@@ -2021,28 +1981,23 @@
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>EC366
+Room: None</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>EC366
+Room: None</t>
+        </is>
+      </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -2055,46 +2010,31 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2104,10 +2044,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>EC366
+Room: None</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>EC366
+Room: None</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>EC366
+Room: None</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>EC366
+Room: None</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -2124,41 +2084,36 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>EC366
 Room: None</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -2350,28 +2305,23 @@
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 102</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>CS372
+Room: 101</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>CS372
+Room: 101</t>
+        </is>
+      </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -2384,46 +2334,31 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 102</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2433,10 +2368,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>CS372
+Room: 101</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>CS372
+Room: 101</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>CS372
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>CS372
+Room: 101</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -2453,41 +2408,36 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>CS372
-Room: 102</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 102</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -2678,10 +2628,30 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
@@ -2690,64 +2660,39 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2777,46 +2722,41 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>EC367
 Room: None</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>EC367
 Room: None</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -2829,10 +2769,30 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -3011,28 +2971,23 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -3042,46 +2997,31 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -3100,25 +3040,20 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>CS371
 Room: None</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>CS371
 Room: None</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
@@ -3126,31 +3061,46 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -3354,38 +3304,53 @@
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -3405,12 +3370,7 @@
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -3420,46 +3380,46 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>CS151
 Room: 101</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>CS151
 Room: 101</t>
         </is>
       </c>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>CS151
 Room: 101</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -3470,26 +3430,31 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -3660,10 +3625,30 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>CS455
+Room: None</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>CS455
+Room: None</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>CS455
+Room: None</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>CS455
+Room: None</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
@@ -3672,64 +3657,39 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>CS455
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>CS455
-Room: None</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>CS455
-Room: None</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>CS455
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>CS455
-Room: 101</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -3759,46 +3719,41 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>CS455
-Room: None</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
+Room: 101</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>CS455
-Room: None</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>CS455
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+Room: 101</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -3811,10 +3766,30 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>CS455
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>CS455
+Room: None</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>CS455
+Room: None</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>CS455
+Room: None</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -3993,28 +3968,23 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -4024,46 +3994,31 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -4082,25 +4037,20 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>EC363
 Room: None</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>EC363
 Room: None</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
@@ -4108,31 +4058,46 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -4323,10 +4288,30 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>CS205
+Room: None</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>CS205
+Room: None</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>CS205
+Room: None</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>CS205
+Room: None</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
@@ -4335,64 +4320,39 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>CS205
-Room: 102</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>CS205
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>CS205
-Room: 102</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>CS205
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>CS205
-Room: 102</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -4422,46 +4382,41 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>CS205
 Room: 102</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>CS205
 Room: 102</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>CS205
-Room: 102</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -4474,10 +4429,30 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>CS205
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>CS205
+Room: None</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>CS205
+Room: None</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>CS205
+Room: None</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -4664,39 +4639,64 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>DS351
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>DS351
+Room: None</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>DS351
+Room: None</t>
+        </is>
+      </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>DS351
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>DS351
+Room: None</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -4705,18 +4705,8 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>DS351
-Room: 102</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>DS351
-Room: 102</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
@@ -4736,31 +4726,31 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -4773,30 +4763,10 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>DS351
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>DS351
-Room: 102</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>DS351
-Room: 102</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>DS351
-Room: 102</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -4991,31 +4961,41 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>ASD351
+Room: 101</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>ASD351
+Room: 101</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -5031,8 +5011,18 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>ASD351
+Room: 101</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>ASD351
+Room: 101</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
@@ -5045,46 +5035,46 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>ASD351
-Room: None</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+Room: 101</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>ASD351
-Room: None</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
+Room: 101</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>ASD351
-Room: None</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+Room: 101</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -5107,24 +5097,9 @@
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>ASD351
-Room: None</t>
-        </is>
-      </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>ASD351
-Room: None</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="inlineStr">
-        <is>
-          <t>ASD351
-Room: None</t>
-        </is>
-      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
@@ -5303,38 +5278,53 @@
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -5354,12 +5344,7 @@
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -5369,46 +5354,46 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>DS151
 Room: 102</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>DS151
 Room: 102</t>
         </is>
       </c>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>DS151
 Room: 102</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -5419,26 +5404,31 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -5613,83 +5603,75 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>DA351
-Room: None</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>DA351
-Room: None</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>DA351
-Room: None</t>
-        </is>
-      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="T3" s="6" t="inlineStr">
         <is>
           <t>nan TUT
 (DSAI_4)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>nan LEC
+(DSAI_4)
 Room: 101</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>DA351
-Room: None</t>
-        </is>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>DA351
-Room: None</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>DA351
-Room: None</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>nan LEC
+(DSAI_4)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -5708,97 +5690,89 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>DA351
 Room: None</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>DA351
 Room: None</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>DA351
 Room: None</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>nan LEC
 (DSAI_4)
 Room: 102</t>
         </is>
       </c>
-      <c r="R5" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>nan LEC
 (DSAI_4)
 Room: 102</t>
         </is>
       </c>
-      <c r="S5" s="5" t="inlineStr">
-        <is>
-          <t>nan LEC
-(DSAI_4)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>nan LEC
-(DSAI_4)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>nan LEC
-(DSAI_4)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
@@ -5999,43 +5973,31 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>EC162 LEC
-(ECE_2)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>EC162 LEC
-(ECE_2)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -6058,50 +6020,80 @@
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>EC162 LEC
+(ECE_2)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>EC162 LEC
+(ECE_2)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>EC162 LEC
+(ECE_2)
+Room: 102</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>EC162 LEC
 (ECE_2)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
+Room: 102</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>EC162 LEC
 (ECE_2)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+Room: 102</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>EC162 LEC
+(ECE_2)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>EC162 LEC
+(ECE_2)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -6304,39 +6296,64 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>DA354
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>DA354
+Room: None</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>DA354
+Room: None</t>
+        </is>
+      </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>DA354
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>DA354
+Room: None</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -6345,18 +6362,8 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>DA354
-Room: None</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>DA354
-Room: None</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
@@ -6376,31 +6383,31 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -6413,30 +6420,10 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>DA354
-Room: None</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>DA354
-Room: None</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>DA354
-Room: None</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>DA354
-Room: None</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -6615,28 +6602,23 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -6646,46 +6628,31 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -6704,25 +6671,20 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>CS370
 Room: None</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>CS370
 Room: None</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
@@ -6730,31 +6692,46 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -6946,28 +6923,23 @@
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>CS472
+Room: None</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>CS472
+Room: None</t>
+        </is>
+      </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -6980,46 +6952,31 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -7029,10 +6986,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>CS472
+Room: None</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>CS472
+Room: None</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>CS472
+Room: None</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>CS472
+Room: None</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -7049,41 +7026,36 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>CS472
 Room: None</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -7286,39 +7258,64 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>DS357
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>DS357
+Room: None</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>DS357
+Room: None</t>
+        </is>
+      </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>DS357
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>DS357
+Room: None</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -7327,18 +7324,8 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>DS357
-Room: None</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>DS357
-Room: None</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
@@ -7358,31 +7345,31 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -7395,30 +7382,10 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>DS357
-Room: None</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>DS357
-Room: None</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>DS357
-Room: None</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>DS357
-Room: None</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -7605,39 +7572,64 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>DS452
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>DS452
+Room: None</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>DS452
+Room: None</t>
+        </is>
+      </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>DS452
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>DS452
+Room: None</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -7646,18 +7638,8 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>DS452
-Room: None</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>DS452
-Room: None</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
@@ -7677,31 +7659,31 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -7714,30 +7696,10 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>DS452
-Room: None</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>DS452
-Room: None</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>DS452
-Room: None</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>DS452
-Room: None</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -7924,39 +7886,64 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>DA353
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>DA353
+Room: None</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>DA353
+Room: None</t>
+        </is>
+      </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>DA353
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>DA353
+Room: None</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -7965,18 +7952,8 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>DA353
-Room: None</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>DA353
-Room: None</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
@@ -7996,31 +7973,31 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -8033,30 +8010,10 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>DA353
-Room: None</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>DA353
-Room: None</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>DA353
-Room: None</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>DA353
-Room: None</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -8235,28 +8192,23 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -8266,46 +8218,31 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -8324,25 +8261,20 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>CS369
 Room: None</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>CS369
 Room: None</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
@@ -8350,31 +8282,46 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -8577,39 +8524,64 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>DA355
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>DA355
+Room: None</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>DA355
+Room: None</t>
+        </is>
+      </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>DA355
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>DA355
+Room: None</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -8618,18 +8590,8 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>DA355
-Room: None</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>DA355
-Room: None</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
@@ -8649,31 +8611,31 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -8686,30 +8648,10 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>DA355
-Room: None</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>DA355
-Room: None</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>DA355
-Room: None</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>DA355
-Room: None</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -8896,39 +8838,69 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>DS358
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>DS358
+Room: None</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>DS358
+Room: None</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>DA151
+Room: None</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>DS358
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>DS358
+Room: None</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -8937,18 +8909,8 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>DS358
-Room: None</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>DS358
-Room: None</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
@@ -8958,12 +8920,7 @@
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>DA151
-Room: None</t>
-        </is>
-      </c>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -8973,46 +8930,46 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>DA151
 Room: None</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>DA151
 Room: None</t>
         </is>
       </c>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>DA151
 Room: None</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -9023,46 +8980,31 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>DS358
-Room: None</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>DS358
-Room: None</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>DS358
-Room: None</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>DS358
-Room: None</t>
-        </is>
-      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>DA151
+Room: None</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>DA151
+Room: None</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>DA151
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>DA151
-Room: None</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>DA151
-Room: None</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -9245,69 +9187,72 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>HS159 LEC
 (CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="inlineStr">
+Room: 102</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>HS159 LEC
 (CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
+Room: 102</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>HS159 LEC
 (CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>HS159 TUT
-(CSE_2_B)
 Room: 102</t>
         </is>
       </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>HS159 TUT
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -9327,12 +9272,7 @@
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>EC155
-Room: None</t>
-        </is>
-      </c>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -9342,46 +9282,52 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>HS159 TUT
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>EC155
 Room: None</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>EC155
 Room: None</t>
         </is>
       </c>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>EC155
 Room: None</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -9392,55 +9338,54 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>HS159 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>HS159 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>HS159 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>HS159 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>EC155
-Room: None</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>EC155
-Room: None</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>HS159 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>HS159 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>HS159 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
@@ -9618,39 +9563,64 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>ASD353+ASD354
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>ASD353+ASD354
+Room: None</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>ASD353+ASD354
+Room: None</t>
+        </is>
+      </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>ASD353+ASD354
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>ASD353+ASD354
+Room: None</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -9659,18 +9629,8 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>ASD353+ASD354
-Room: None</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>ASD353+ASD354
-Room: None</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
@@ -9690,31 +9650,31 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -9727,30 +9687,10 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>ASD353+ASD354
-Room: None</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>ASD353+ASD354
-Room: None</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>ASD353+ASD354
-Room: None</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>ASD353+ASD354
-Room: None</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -9924,30 +9864,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>EC257
+Room: 102</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>EC257
+Room: 102</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>CS464
+Room: None</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>CS464
+Room: None</t>
+        </is>
+      </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -9960,46 +9905,51 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>EC257
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>EC257
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>EC257
+Room: 102</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>EC257
+Room: 102</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -10009,28 +9959,28 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>EC257
-Room: 101</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>EC257
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>EC257
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>EC257
-Room: 101</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>CS464
+Room: None</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>CS464
+Room: None</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>CS464
+Room: None</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>CS464
+Room: None</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
@@ -10049,61 +9999,36 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>CS464
 Room: None</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>EC257
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>EC257
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>EC257
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>EC257
-Room: 101</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -10123,22 +10048,17 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>EC257
+Room: 101</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>EC257
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>EC257
-Room: 101</t>
-        </is>
-      </c>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
@@ -10308,28 +10228,23 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 101</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 101</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 101</t>
-        </is>
-      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>EC456
+Room: 102</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>EC456
+Room: 102</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -10339,46 +10254,31 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 101</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -10397,25 +10297,20 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>EC456
-Room: 101</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
+Room: 102</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>EC456
-Room: 101</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 101</t>
-        </is>
-      </c>
+Room: 102</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
@@ -10423,31 +10318,46 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>EC456
+Room: 102</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>EC456
+Room: 102</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>EC456
+Room: 102</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -10638,105 +10548,130 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
 (DSAI_4)
 Room: 101</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
 (DSAI_4)
 Room: 101</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
 (DSAI_4)
 Room: 101</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
 (DSAI_4)
 Room: 101</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>DS308 LEC
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>CS373
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>CS373
+Room: None</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>CS373
+Room: None</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>DS308 TUT
 (DSAI_6)
 Room: 101</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>DS308 LEC
-(DSAI_6)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>DS308 TUT
 (CSE_6_B)
 Room: 102</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>CS373
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>CS373
+Room: None</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
 (DSAI_4)
 Room: 101</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
 (DSAI_4)
 Room: 101</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>DS308 LEC
+(DSAI_4)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -10745,57 +10680,41 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>CS373
-Room: None</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>CS373
-Room: None</t>
-        </is>
-      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>DS308 TUT
+(DSAI_4)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>DS308 TUT
-(DSAI_4)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>DS308 TUT
-(DSAI_4)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
 (CSE_6_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="R5" s="5" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
 (CSE_6_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="S5" s="5" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
 (CSE_6_B)
@@ -10806,31 +10725,31 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -10839,62 +10758,54 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
-(CSE_6_B)
+(DSAI_6)
 Room: 101</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
-(CSE_6_B)
+(DSAI_6)
 Room: 101</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>CS373
-Room: None</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>CS373
-Room: None</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>CS373
-Room: None</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>CS373
-Room: None</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="6" t="inlineStr">
-        <is>
-          <t>DS308 TUT
-(DSAI_6)
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>DS308 LEC
+(CSE_6_B)
 Room: 101</t>
         </is>
       </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>DS308 LEC
+(CSE_6_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>DS308 LEC
+(CSE_6_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
@@ -11068,20 +10979,8 @@
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>EC307 LEC
-(ECE_6)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>EC307 LEC
-(ECE_6)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -11091,31 +10990,59 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>EC361
+Room: None</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>EC361
+Room: None</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>EC307 LEC
+(ECE_6)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>EC307 LEC
+(ECE_6)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>EC307 LEC
+(ECE_6)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -11131,8 +11058,18 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>EC361
+Room: 102</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>EC361
+Room: 102</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
@@ -11145,46 +11082,46 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>EC361
 Room: None</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>EC361
 Room: None</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>EC361
 Room: None</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -11193,20 +11130,8 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>EC307 LEC
-(ECE_6)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>EC307 LEC
-(ECE_6)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
@@ -11219,24 +11144,9 @@
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>EC361
-Room: None</t>
-        </is>
-      </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>EC361
-Room: None</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="inlineStr">
-        <is>
-          <t>EC361
-Room: None</t>
-        </is>
-      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
@@ -11402,10 +11312,30 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
@@ -11414,64 +11344,39 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -11501,46 +11406,41 @@
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>CS458
 Room: None</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>CS458
 Room: None</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -11553,10 +11453,30 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>

--- a/tests/TC-01/results/teacher_timetables_even.xlsx
+++ b/tests/TC-01/results/teacher_timetables_even.xlsx
@@ -39,7 +39,8 @@
     <sheet name="Dr. Vivekraj" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="Prof. Arulalan Rajan" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="Prof. S R M Prasanna" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="TBD" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="TBD_B2-EC155" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="TBD_HS159" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -648,24 +649,34 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>CS252
 Room: 101</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>CS252
 Room: 101</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>CS252
+Room: 101</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>CS252
+Room: 101</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
@@ -687,31 +698,26 @@
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>CS252
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+Room: 102</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>CS252
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>CS252
-Room: 101</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>CS252
-Room: 101</t>
-        </is>
-      </c>
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
@@ -763,10 +769,30 @@
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>CS252
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>CS252
+Room: 101</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>CS252
+Room: 101</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>CS252
+Room: 101</t>
+        </is>
+      </c>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
@@ -797,12 +823,7 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>CS252
-Room: 102</t>
-        </is>
-      </c>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -979,18 +1000,8 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 102</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 102</t>
-        </is>
-      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -1020,9 +1031,24 @@
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>CS469
+Room: 101</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>CS469
+Room: 101</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>CS469
+Room: 101</t>
+        </is>
+      </c>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
@@ -1037,30 +1063,10 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 102</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 102</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -1087,12 +1093,7 @@
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>CS469
-Room: 102</t>
-        </is>
-      </c>
+      <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
@@ -1101,9 +1102,24 @@
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>CS469
+Room: 101</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>CS469
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>CS469
+Room: 101</t>
+        </is>
+      </c>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
@@ -1115,7 +1131,12 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>CS469
+Room: 102</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
@@ -1309,8 +1330,18 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>DA352
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>DA352
+Room: None</t>
+        </is>
+      </c>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
@@ -1333,18 +1364,8 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>DA352
-Room: None</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>DA352
-Room: None</t>
-        </is>
-      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
@@ -1408,24 +1429,9 @@
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>DA352
-Room: None</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>DA352
-Room: None</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>DA352
-Room: None</t>
-        </is>
-      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
@@ -1452,9 +1458,24 @@
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>DA352
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>DA352
+Room: None</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>DA352
+Room: None</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
@@ -1620,38 +1641,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>CS368
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>CS368
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>CS368
+Room: 102</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>CS368
+Room: 102</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> CS253
 Room: None</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CS253
-Room: None</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>CS368
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>CS368
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -1669,31 +1695,26 @@
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> CS253
 Room: None</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> CS253
 Room: None</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> CS253
 Room: None</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CS253
-Room: None</t>
-        </is>
-      </c>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
@@ -1724,23 +1745,28 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>CS368
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>CS368
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>CS368
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>CS368
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>CS368
+Room: 102</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -1755,23 +1781,28 @@
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>CS368
-Room: 101</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>CS368
-Room: 101</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>CS368
-Room: 101</t>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CS253
+Room: None</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CS253
+Room: None</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CS253
+Room: None</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CS253
+Room: None</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr"/>
@@ -1797,19 +1828,29 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CS368
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>CS368
+Room: None</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CS368
+Room: None</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CS253
-Room: None</t>
-        </is>
-      </c>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -1986,18 +2027,8 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -2027,9 +2058,24 @@
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>EC366
+Room: None</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>EC366
+Room: None</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>EC366
+Room: None</t>
+        </is>
+      </c>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
@@ -2044,30 +2090,10 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -2094,12 +2120,7 @@
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>EC366
-Room: None</t>
-        </is>
-      </c>
+      <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
@@ -2108,9 +2129,24 @@
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>EC366
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>EC366
+Room: None</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>EC366
+Room: None</t>
+        </is>
+      </c>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
@@ -2122,7 +2158,12 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>EC366
+Room: None</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
@@ -2310,18 +2351,8 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 101</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 101</t>
-        </is>
-      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -2351,9 +2382,24 @@
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>CS372
+Room: 102</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>CS372
+Room: 102</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>CS372
+Room: 102</t>
+        </is>
+      </c>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
@@ -2368,30 +2414,10 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 101</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 101</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -2418,12 +2444,7 @@
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>CS372
-Room: 101</t>
-        </is>
-      </c>
+      <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
@@ -2432,9 +2453,24 @@
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>CS372
+Room: 102</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>CS372
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>CS372
+Room: 102</t>
+        </is>
+      </c>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
@@ -2446,7 +2482,12 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>CS372
+Room: 101</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
@@ -2628,30 +2669,10 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
@@ -2662,8 +2683,18 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -2676,10 +2707,30 @@
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>EC367
+Room: None</t>
+        </is>
+      </c>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -2728,18 +2779,8 @@
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
@@ -2768,31 +2809,16 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>EC367
 Room: None</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>EC367
-Room: None</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -2969,25 +2995,35 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -3040,23 +3076,28 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -3072,24 +3113,9 @@
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>CS371
-Room: None</t>
-        </is>
-      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
@@ -3113,9 +3139,24 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CS371
+Room: None</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
@@ -3304,24 +3345,9 @@
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -3360,10 +3386,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -3387,9 +3433,24 @@
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 102</t>
+        </is>
+      </c>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
@@ -3399,24 +3460,9 @@
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
@@ -3430,26 +3476,31 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>CS151
 Room: 101</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>CS151
 Room: 101</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>CS151
 Room: 101</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
@@ -3625,30 +3676,10 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>CS455
-Room: None</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>CS455
-Room: None</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CS455
-Room: None</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>CS455
-Room: None</t>
-        </is>
-      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
@@ -3659,8 +3690,18 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>CS455
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>CS455
+Room: 101</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -3673,10 +3714,30 @@
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>CS455
+Room: None</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>CS455
+Room: None</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>CS455
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>CS455
+Room: None</t>
+        </is>
+      </c>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -3725,18 +3786,8 @@
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>CS455
-Room: 101</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>CS455
-Room: 101</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
@@ -3765,31 +3816,16 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>CS455
 Room: None</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>CS455
-Room: None</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>CS455
-Room: None</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>CS455
-Room: None</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -3966,25 +4002,35 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -4037,23 +4083,28 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -4069,24 +4120,9 @@
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>EC363
-Room: None</t>
-        </is>
-      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
@@ -4110,9 +4146,24 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>EC363
+Room: None</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
@@ -4288,30 +4339,10 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>CS205
-Room: None</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>CS205
-Room: None</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CS205
-Room: None</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>CS205
-Room: None</t>
-        </is>
-      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
@@ -4322,8 +4353,18 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>CS205
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>CS205
+Room: 102</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -4336,10 +4377,30 @@
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>CS205
+Room: None</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>CS205
+Room: None</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>CS205
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>CS205
+Room: None</t>
+        </is>
+      </c>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -4388,18 +4449,8 @@
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>CS205
-Room: 102</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>CS205
-Room: 102</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
@@ -4428,31 +4479,16 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>CS205
 Room: None</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>CS205
-Room: None</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>CS205
-Room: None</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>CS205
-Room: None</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -4626,8 +4662,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>DS351
+Room: 101</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>DS351
+Room: 101</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -4639,24 +4685,9 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>DS351
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>DS351
-Room: None</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>DS351
-Room: None</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
@@ -4672,18 +4703,8 @@
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>DS351
-Room: None</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>DS351
-Room: None</t>
-        </is>
-      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -4735,10 +4756,30 @@
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>DS351
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>DS351
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>DS351
+Room: 101</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>DS351
+Room: 101</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
@@ -4761,7 +4802,12 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>DS351
+Room: None</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -4953,8 +4999,18 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>ASD351
+Room: 102</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>ASD351
+Room: 102</t>
+        </is>
+      </c>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
@@ -4977,18 +5033,8 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>ASD351
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>ASD351
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
@@ -5052,24 +5098,9 @@
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>ASD351
-Room: 101</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>ASD351
-Room: 101</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>ASD351
-Room: 101</t>
-        </is>
-      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
@@ -5096,9 +5127,24 @@
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>ASD351
+Room: 102</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>ASD351
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>ASD351
+Room: 102</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
@@ -5278,24 +5324,9 @@
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -5334,10 +5365,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -5361,9 +5412,24 @@
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 101</t>
+        </is>
+      </c>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
@@ -5373,24 +5439,9 @@
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
@@ -5404,26 +5455,31 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>DS151
 Room: 102</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>DS151
 Room: 102</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>DS151
 Room: 102</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
@@ -5601,58 +5657,62 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>DA351
-Room: None</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>DA351
-Room: None</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr">
-        <is>
-          <t>nan TUT
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>nan LEC
 (DSAI_4)
 Room: 102</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>nan LEC
 (DSAI_4)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>nan LEC
-(DSAI_4)
-Room: 101</t>
+Room: 102</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr"/>
@@ -5680,7 +5740,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>nan TUT
+(DSAI_4)
+Room: 101</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
@@ -5690,23 +5756,28 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>DA351
-Room: None</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>DA351
-Room: None</t>
-        </is>
-      </c>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -5722,28 +5793,25 @@
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>DA351
-Room: None</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>DA351
-Room: None</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>DA351
-Room: None</t>
-        </is>
-      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>nan LEC
+(DSAI_4)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>nan LEC
+(DSAI_4)
+Room: 101</t>
+        </is>
+      </c>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
@@ -5759,25 +5827,28 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>nan LEC
-(DSAI_4)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>nan LEC
-(DSAI_4)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>DA351
+Room: None</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
@@ -5993,9 +6064,27 @@
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>EC162 LEC
+(ECE_2)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>EC162 LEC
+(ECE_2)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>EC162 LEC
+(ECE_2)
+Room: 101</t>
+        </is>
+      </c>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -6020,27 +6109,9 @@
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>EC162 LEC
-(ECE_2)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>EC162 LEC
-(ECE_2)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>EC162 LEC
-(ECE_2)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -6052,34 +6123,10 @@
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>EC162 LEC
-(ECE_2)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>EC162 LEC
-(ECE_2)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>EC162 LEC
-(ECE_2)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>EC162 LEC
-(ECE_2)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
@@ -6112,8 +6159,20 @@
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>EC162 LEC
+(ECE_2)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>EC162 LEC
+(ECE_2)
+Room: 102</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -6283,8 +6342,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>DA354
+Room: None</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>DA354
+Room: None</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -6296,24 +6365,9 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>DA354
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>DA354
-Room: None</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>DA354
-Room: None</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
@@ -6329,18 +6383,8 @@
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>DA354
-Room: None</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>DA354
-Room: None</t>
-        </is>
-      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -6392,10 +6436,30 @@
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>DA354
+Room: None</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>DA354
+Room: None</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>DA354
+Room: None</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>DA354
+Room: None</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
@@ -6418,7 +6482,12 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>DA354
+Room: None</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -6600,25 +6669,35 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -6671,23 +6750,28 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -6703,24 +6787,9 @@
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>CS370
-Room: None</t>
-        </is>
-      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
@@ -6744,9 +6813,24 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CS370
+Room: None</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
@@ -6928,18 +7012,8 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -6969,9 +7043,24 @@
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>CS472
+Room: None</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>CS472
+Room: None</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>CS472
+Room: None</t>
+        </is>
+      </c>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
@@ -6986,30 +7075,10 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -7036,12 +7105,7 @@
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>CS472
-Room: None</t>
-        </is>
-      </c>
+      <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
@@ -7050,9 +7114,24 @@
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>CS472
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>CS472
+Room: None</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>CS472
+Room: None</t>
+        </is>
+      </c>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
@@ -7064,7 +7143,12 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>CS472
+Room: None</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
@@ -7245,8 +7329,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>DS357
+Room: None</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>DS357
+Room: None</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -7258,24 +7352,9 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>DS357
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>DS357
-Room: None</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>DS357
-Room: None</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
@@ -7291,18 +7370,8 @@
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>DS357
-Room: None</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>DS357
-Room: None</t>
-        </is>
-      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -7354,10 +7423,30 @@
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>DS357
+Room: None</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>DS357
+Room: None</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>DS357
+Room: None</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>DS357
+Room: None</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
@@ -7380,7 +7469,12 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>DS357
+Room: None</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -7559,8 +7653,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>DS452
+Room: 102</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>DS452
+Room: 102</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -7572,24 +7676,9 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>DS452
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>DS452
-Room: None</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>DS452
-Room: None</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
@@ -7605,18 +7694,8 @@
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>DS452
-Room: None</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>DS452
-Room: None</t>
-        </is>
-      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -7668,10 +7747,30 @@
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>DS452
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>DS452
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>DS452
+Room: 102</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>DS452
+Room: 102</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
@@ -7694,7 +7793,12 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>DS452
+Room: None</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -7873,8 +7977,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>DA353
+Room: None</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>DA353
+Room: None</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -7886,24 +8000,9 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>DA353
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>DA353
-Room: None</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>DA353
-Room: None</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
@@ -7919,18 +8018,8 @@
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>DA353
-Room: None</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>DA353
-Room: None</t>
-        </is>
-      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -7982,10 +8071,30 @@
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>DA353
+Room: None</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>DA353
+Room: None</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>DA353
+Room: None</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>DA353
+Room: None</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
@@ -8008,7 +8117,12 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>DA353
+Room: None</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -8190,25 +8304,35 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -8261,23 +8385,28 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -8293,24 +8422,9 @@
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>CS369
-Room: None</t>
-        </is>
-      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
@@ -8334,9 +8448,24 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CS369
+Room: None</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
@@ -8511,8 +8640,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>DA355
+Room: None</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>DA355
+Room: None</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -8524,24 +8663,9 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>DA355
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>DA355
-Room: None</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>DA355
-Room: None</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
@@ -8557,18 +8681,8 @@
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>DA355
-Room: None</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>DA355
-Room: None</t>
-        </is>
-      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -8620,10 +8734,30 @@
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>DA355
+Room: None</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>DA355
+Room: None</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>DA355
+Room: None</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>DA355
+Room: None</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
@@ -8646,7 +8780,12 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>DA355
+Room: None</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -8825,8 +8964,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>DS358
+Room: None</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>DS358
+Room: None</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -8838,30 +8987,10 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>DS358
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>DS358
-Room: None</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>DS358
-Room: None</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>DA151
-Room: None</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -8876,18 +9005,8 @@
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>DS358
-Room: None</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>DS358
-Room: None</t>
-        </is>
-      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -8910,10 +9029,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>DA151
+Room: None</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>DA151
+Room: None</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>DA151
+Room: None</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>DA151
+Room: None</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -8937,36 +9076,51 @@
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>DA151
+Room: None</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>DA151
+Room: None</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>DS358
+Room: None</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>DS358
+Room: None</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>DS358
+Room: None</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>DS358
+Room: None</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>DA151
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>DA151
-Room: None</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>DA151
-Room: None</t>
-        </is>
-      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
@@ -8982,24 +9136,34 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr">
         <is>
+          <t>DS358
+Room: None</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>DA151
 Room: None</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>DA151
 Room: None</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>DA151
 Room: None</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>DA151
+Room: None</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
@@ -9022,6 +9186,350 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TBD_B2-EC155  Weekly Timetable</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>07:30-09:00</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>10:00-10:30</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>10:45-11:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>11:00-11:30</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>11:30-12:00</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>12:00-12:15</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>12:30-13:15</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>13:15-14:00</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>15:30-15:40</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>15:40-16:00</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>16:00-16:30</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>16:30-17:10</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>17:10-17:30</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>17:30-18:30</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>18:30-20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="35" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>EC155
+Room: None</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:U1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9056,7 +9564,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TBD  Weekly Timetable</t>
+          <t>TBD_HS159  Weekly Timetable</t>
         </is>
       </c>
     </row>
@@ -9185,27 +9693,18 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>HS159 TUT
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>EC155
-Room: None</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>EC155
-Room: None</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>EC155
-Room: None</t>
-        </is>
-      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -9227,27 +9726,9 @@
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>HS159 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>HS159 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>HS159 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
@@ -9272,9 +9753,27 @@
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>HS159 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>HS159 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>HS159 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
@@ -9292,39 +9791,42 @@
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>HS159 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>HS159 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>HS159 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>HS159 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>HS159 TUT
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>EC155
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>EC155
-Room: None</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>EC155
-Room: None</t>
-        </is>
-      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
@@ -9338,24 +9840,9 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>EC155
-Room: None</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>EC155
-Room: None</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>EC155
-Room: None</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
@@ -9365,27 +9852,9 @@
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>HS159 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R7" s="4" t="inlineStr">
-        <is>
-          <t>HS159 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="S7" s="4" t="inlineStr">
-        <is>
-          <t>HS159 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
@@ -9550,8 +10019,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ASD353+ASD354
+Room: None</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ASD353+ASD354
+Room: None</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -9563,24 +10042,9 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>ASD353+ASD354
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>ASD353+ASD354
-Room: None</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>ASD353+ASD354
-Room: None</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
@@ -9596,18 +10060,8 @@
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>ASD353+ASD354
-Room: None</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>ASD353+ASD354
-Room: None</t>
-        </is>
-      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -9659,10 +10113,30 @@
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>ASD353+ASD354
+Room: None</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>ASD353+ASD354
+Room: None</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>ASD353+ASD354
+Room: None</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>ASD353+ASD354
+Room: None</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
@@ -9685,7 +10159,12 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>ASD353+ASD354
+Room: None</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -9864,35 +10343,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>EC257
 Room: 102</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>EC257
 Room: 102</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>EC257
+Room: 102</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>EC257
+Room: 102</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
@@ -9913,38 +10392,48 @@
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>EC257
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+Room: 101</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>EC257
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>EC257
-Room: 102</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>EC257
-Room: 102</t>
-        </is>
-      </c>
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>CS464
+Room: None</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>CS464
+Room: None</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>CS464
+Room: None</t>
+        </is>
+      </c>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
@@ -9959,30 +10448,10 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -10011,21 +10480,51 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>CS464
-Room: None</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
+          <t>EC257
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>EC257
+Room: 102</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>EC257
+Room: 102</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>EC257
+Room: 102</t>
+        </is>
+      </c>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>CS464
+Room: None</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>CS464
+Room: None</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>CS464
+Room: None</t>
+        </is>
+      </c>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
@@ -10037,7 +10536,12 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>CS464
+Room: None</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
@@ -10048,12 +10552,7 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>EC257
-Room: 101</t>
-        </is>
-      </c>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -10226,25 +10725,35 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>EC456
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>EC456
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>EC456
+Room: 101</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>EC456
+Room: 101</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 102</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 102</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -10297,23 +10806,28 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 102</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 102</t>
-        </is>
-      </c>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>EC456
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>EC456
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>EC456
+Room: 101</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -10329,24 +10843,9 @@
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 102</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 102</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>EC456
-Room: 102</t>
-        </is>
-      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
@@ -10370,9 +10869,24 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>EC456
+Room: None</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>EC456
+Room: None</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>EC456
+Room: None</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
@@ -10547,67 +11061,50 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>CS373
+Room: None</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>CS373
+Room: None</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>DS308 LEC
-(DSAI_4)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>DS308 LEC
-(DSAI_4)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>DS308 LEC
-(DSAI_4)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>DS308 LEC
-(DSAI_4)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>DS308 LEC
+(CSE_6_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>DS308 LEC
+(CSE_6_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>CS373
-Room: None</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>CS373
-Room: None</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>CS373
-Room: None</t>
-        </is>
-      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="6" t="inlineStr">
         <is>
           <t>DS308 TUT
 (DSAI_6)
-Room: 101</t>
+Room: 102</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr"/>
@@ -10619,28 +11116,24 @@
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>DS308 TUT
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>DS308 LEC
 (CSE_6_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr"/>
+Room: 101</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>DS308 LEC
+(CSE_6_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>CS373
-Room: None</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>CS373
-Room: None</t>
-        </is>
-      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -10648,45 +11141,33 @@
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>DS308 LEC
-(DSAI_4)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>DS308 LEC
-(DSAI_4)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>DS308 LEC
-(DSAI_4)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>DS308 TUT
 (DSAI_4)
 Room: 102</t>
         </is>
       </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>DS308 TUT
+(DSAI_4)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
@@ -10697,30 +11178,30 @@
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
-(CSE_6_B)
+(DSAI_4)
 Room: 101</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
-(CSE_6_B)
+(DSAI_4)
 Room: 101</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>DS308 LEC
-(CSE_6_B)
+(DSAI_4)
 Room: 101</t>
         </is>
       </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -10734,15 +11215,41 @@
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>CS373
+Room: None</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>CS373
+Room: None</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>CS373
+Room: None</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>CS373
+Room: None</t>
+        </is>
+      </c>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>DS308 TUT
+(CSE_6_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
@@ -10758,21 +11265,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>DS308 LEC
-(DSAI_6)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>DS308 LEC
-(DSAI_6)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>CS373
+Room: None</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
@@ -10780,31 +11280,25 @@
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>DS308 LEC
+(DSAI_4)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>DS308 LEC
+(DSAI_4)
+Room: 101</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>DS308 LEC
-(CSE_6_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R7" s="4" t="inlineStr">
-        <is>
-          <t>DS308 LEC
-(CSE_6_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S7" s="4" t="inlineStr">
-        <is>
-          <t>DS308 LEC
-(CSE_6_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
@@ -10982,8 +11476,18 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>EC361
+Room: 101</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>EC361
+Room: 101</t>
+        </is>
+      </c>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
@@ -11006,41 +11510,13 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>EC361
-Room: None</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>EC361
-Room: None</t>
-        </is>
-      </c>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>EC307 LEC
-(ECE_6)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>EC307 LEC
-(ECE_6)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>EC307 LEC
-(ECE_6)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -11099,24 +11575,9 @@
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>EC361
-Room: None</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>EC361
-Room: None</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>EC361
-Room: None</t>
-        </is>
-      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
@@ -11143,9 +11604,24 @@
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>EC361
+Room: 101</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>EC361
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>EC361
+Room: 101</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
@@ -11312,30 +11788,10 @@
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
@@ -11346,8 +11802,18 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -11360,10 +11826,30 @@
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>CS458
+Room: None</t>
+        </is>
+      </c>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -11412,18 +11898,8 @@
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
@@ -11452,31 +11928,16 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>CS458
 Room: None</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>CS458
-Room: None</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
